--- a/backend/data/financials_by_company/1EL.F.xlsx
+++ b/backend/data/financials_by_company/1EL.F.xlsx
@@ -615,10 +615,10 @@
         <v>146869000</v>
       </c>
       <c r="L2" t="n">
-        <v>99437979</v>
+        <v>100529000</v>
       </c>
       <c r="M2" t="n">
-        <v>99437979</v>
+        <v>99438000</v>
       </c>
       <c r="N2" t="n">
         <v>1.19</v>
@@ -2673,177 +2673,177 @@
       </c>
       <c r="AX1" t="inlineStr">
         <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>priceToBook</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>marketCap</t>
-        </is>
-      </c>
-      <c r="BZ1" t="inlineStr">
-        <is>
-          <t>priceToBook</t>
-        </is>
-      </c>
-      <c r="CA1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="CB1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="CC1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="CD1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="CE1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="CF1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
@@ -2860,55 +2860,55 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>11.52</v>
+        <v>11.65</v>
       </c>
       <c r="D2" t="n">
-        <v>11.55</v>
+        <v>11.65</v>
       </c>
       <c r="E2" t="n">
-        <v>11.55</v>
+        <v>11.65</v>
       </c>
       <c r="F2" t="n">
         <v>11.65</v>
       </c>
       <c r="G2" t="n">
-        <v>11.52</v>
+        <v>11.65</v>
       </c>
       <c r="H2" t="n">
-        <v>11.55</v>
+        <v>11.65</v>
       </c>
       <c r="I2" t="n">
-        <v>11.55</v>
+        <v>11.65</v>
       </c>
       <c r="J2" t="n">
         <v>11.65</v>
       </c>
       <c r="K2" t="n">
-        <v>8.381295</v>
+        <v>8.262411</v>
       </c>
       <c r="L2" t="n">
         <v>6.164021</v>
       </c>
       <c r="M2" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="N2" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="O2" t="n">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="P2" t="n">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="Q2" t="n">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="R2" t="n">
-        <v>11.65</v>
+        <v>11.75</v>
       </c>
       <c r="S2" t="n">
-        <v>11.75</v>
+        <v>11.8</v>
       </c>
       <c r="T2" t="n">
         <v>9.695</v>
@@ -2923,16 +2923,16 @@
         <v>3.4</v>
       </c>
       <c r="X2" t="n">
-        <v>11.04</v>
+        <v>11.4182</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.265875</v>
+        <v>11.266275</v>
       </c>
       <c r="Z2" t="n">
         <v>1.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.13541666</v>
+        <v>0.13390557</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>1780430102</v>
+        <v>1782108602</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.1284649</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
         <v>11.65</v>
@@ -3032,120 +3032,120 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>0.12999916</v>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>11.55 - 11.65</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
+          <t>Ellington Financial Inc.</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.9803195</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1564120800000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>11.65 - 11.65</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
         <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="BC2" t="n">
-        <v>974</v>
-      </c>
-      <c r="BD2" t="n">
+      <c r="BJ2" t="n">
+        <v>982</v>
+      </c>
+      <c r="BK2" t="n">
         <v>1.9549999</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BL2" t="n">
         <v>0.20165034</v>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>9.695 - 12.05</t>
         </is>
       </c>
-      <c r="BG2" t="n">
+      <c r="BN2" t="n">
         <v>-0.40000057</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BO2" t="n">
         <v>-0.033195067</v>
       </c>
-      <c r="BI2" t="n">
-        <v>5.3016424</v>
-      </c>
-      <c r="BJ2" t="n">
+      <c r="BP2" t="n">
+        <v>4.5781016</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>1778011200</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BR2" t="n">
         <v>1778011200</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BS2" t="n">
         <v>1778011200</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BT2" t="n">
         <v>1778079600</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BU2" t="n">
         <v>1778079600</v>
       </c>
-      <c r="BO2" t="b">
+      <c r="BV2" t="b">
         <v>0</v>
       </c>
-      <c r="BP2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BQ2" t="n">
+      <c r="BW2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BX2" t="n">
         <v>1.89</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="BY2" t="n">
         <v>125393624</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="BZ2" t="n">
         <v>125393624</v>
       </c>
-      <c r="BT2" t="n">
-        <v>11.703297</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.6099996600000001</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0.05525359</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0.38412476</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.034096308</v>
-      </c>
-      <c r="BY2" t="n">
+      <c r="CA2" t="n">
+        <v>11.883881</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>0.23180008</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>0.02030093</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.3837242</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>0.034059543</v>
+      </c>
+      <c r="CF2" t="n">
         <v>1460835712</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.99544597</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>15</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>15</v>
-      </c>
-      <c r="CC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CD2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>1564120800000</v>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>Ellington Financial Inc.</t>
-        </is>
       </c>
       <c r="CG2" t="inlineStr"/>
     </row>
